--- a/figs/table1.xlsx
+++ b/figs/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/arjun_chakrawal_pnnl_gov/Documents/MONet/DynamicDRmodel/chemodiv-litter-model/figs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_0811B1B8D3C0D34AAB1B2B11595ED87656CD3477" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{311F2C56-549E-4B28-9814-04E95FAA0666}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_3FA992AAD350D83D6B383911595ED87656CD9462" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F0531A6-FD47-45CC-B8D6-36EBEB44BE41}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="215">
   <si>
     <t>Study</t>
   </si>
@@ -70,6 +70,9 @@
     <t>168.00</t>
   </si>
   <si>
+    <t>14.50</t>
+  </si>
+  <si>
     <t>415.00</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>180.00</t>
   </si>
   <si>
+    <t>16.50</t>
+  </si>
+  <si>
     <t>1080.00</t>
   </si>
   <si>
@@ -145,6 +151,9 @@
     <t>720.00</t>
   </si>
   <si>
+    <t>9.20</t>
+  </si>
+  <si>
     <t>1273.00</t>
   </si>
   <si>
@@ -181,6 +190,9 @@
     <t>403.00 - 810.00</t>
   </si>
   <si>
+    <t>16.00</t>
+  </si>
+  <si>
     <t>756.00</t>
   </si>
   <si>
@@ -217,6 +229,9 @@
     <t>360.00</t>
   </si>
   <si>
+    <t>15.50</t>
+  </si>
+  <si>
     <t>985.00</t>
   </si>
   <si>
@@ -256,6 +271,9 @@
     <t>600.00</t>
   </si>
   <si>
+    <t>13.90</t>
+  </si>
+  <si>
     <t>597.00</t>
   </si>
   <si>
@@ -289,6 +307,9 @@
     <t>562.00</t>
   </si>
   <si>
+    <t>21.00</t>
+  </si>
+  <si>
     <t>516.00</t>
   </si>
   <si>
@@ -325,6 +346,9 @@
     <t>1096.00</t>
   </si>
   <si>
+    <t>12.80</t>
+  </si>
+  <si>
     <t>835.00</t>
   </si>
   <si>
@@ -358,6 +382,9 @@
     <t>1095.00</t>
   </si>
   <si>
+    <t>10.70</t>
+  </si>
+  <si>
     <t>2031.00</t>
   </si>
   <si>
@@ -382,36 +409,42 @@
     <t>0.20 - 0.22</t>
   </si>
   <si>
+    <t>Ono et al 2011</t>
+  </si>
+  <si>
+    <t>13.70</t>
+  </si>
+  <si>
+    <t>1400.00</t>
+  </si>
+  <si>
+    <t>592.70 - 609.40</t>
+  </si>
+  <si>
+    <t>10.62 - 11.14</t>
+  </si>
+  <si>
+    <t>53.20 - 57.40</t>
+  </si>
+  <si>
+    <t>0.37 - 0.39</t>
+  </si>
+  <si>
+    <t>0.24 - 0.26</t>
+  </si>
+  <si>
+    <t>0.31 - 0.32</t>
+  </si>
+  <si>
     <t>0.00 - 0.00</t>
   </si>
   <si>
-    <t>Ono et al 2011</t>
-  </si>
-  <si>
-    <t>1400.00</t>
-  </si>
-  <si>
-    <t>592.70 - 609.40</t>
-  </si>
-  <si>
-    <t>10.62 - 11.14</t>
-  </si>
-  <si>
-    <t>53.20 - 57.40</t>
-  </si>
-  <si>
-    <t>0.37 - 0.39</t>
-  </si>
-  <si>
-    <t>0.24 - 0.26</t>
-  </si>
-  <si>
-    <t>0.31 - 0.32</t>
-  </si>
-  <si>
     <t>Ono et al 2013</t>
   </si>
   <si>
+    <t>9.10 - 22.90</t>
+  </si>
+  <si>
     <t>1111.00 - 2204.00</t>
   </si>
   <si>
@@ -463,6 +496,9 @@
     <t>2190.00</t>
   </si>
   <si>
+    <t>6.70</t>
+  </si>
+  <si>
     <t>978.00</t>
   </si>
   <si>
@@ -502,6 +538,9 @@
     <t>733.00</t>
   </si>
   <si>
+    <t>14.40</t>
+  </si>
+  <si>
     <t>678.00</t>
   </si>
   <si>
@@ -535,6 +574,9 @@
     <t>559.00</t>
   </si>
   <si>
+    <t>7.60</t>
+  </si>
+  <si>
     <t>1440.00</t>
   </si>
   <si>
@@ -595,6 +637,9 @@
     <t>450.00</t>
   </si>
   <si>
+    <t>19.88</t>
+  </si>
+  <si>
     <t>1000.00</t>
   </si>
   <si>
@@ -620,9 +665,6 @@
   </si>
   <si>
     <t>0.01 - 0.03</t>
-  </si>
-  <si>
-    <t>9.2-22.5</t>
   </si>
 </sst>
 </file>
@@ -678,12 +720,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,10 +740,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -992,6 +1029,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
@@ -1047,41 +1098,41 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2">
-        <v>14.5</v>
+      <c r="D2" t="s">
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -1089,46 +1140,46 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>16.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1136,46 +1187,46 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4">
-        <v>9.1999999999999993</v>
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1183,46 +1234,46 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5">
-        <v>16</v>
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -1230,46 +1281,46 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6">
-        <v>15.5</v>
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="M6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -1277,46 +1328,46 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7">
-        <v>13.9</v>
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>83</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" t="s">
         <v>79</v>
       </c>
-      <c r="G7" t="s">
+      <c r="O7" t="s">
         <v>80</v>
-      </c>
-      <c r="H7" t="s">
-        <v>81</v>
-      </c>
-      <c r="I7" t="s">
-        <v>82</v>
-      </c>
-      <c r="J7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" t="s">
-        <v>84</v>
-      </c>
-      <c r="L7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M7" t="s">
-        <v>86</v>
-      </c>
-      <c r="N7" t="s">
-        <v>74</v>
-      </c>
-      <c r="O7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -1324,46 +1375,46 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8">
-        <v>21</v>
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="M8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="O8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1371,46 +1422,46 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>12.8</v>
+        <v>107</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F9" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J9" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K9" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="L9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="N9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1418,46 +1469,46 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10">
-        <v>10.7</v>
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H10" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I10" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J10" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K10" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="N10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1465,46 +1516,46 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11">
-        <v>13.7</v>
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G11" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="J11" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K11" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="M11" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="N11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1512,46 +1563,46 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>200</v>
+        <v>119</v>
+      </c>
+      <c r="D12" t="s">
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G12" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="H12" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="N12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O12" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1559,46 +1610,46 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13">
-        <v>9.1999999999999993</v>
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H13" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I13" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J13" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="N13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1606,46 +1657,46 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14">
-        <v>6.7</v>
+        <v>157</v>
+      </c>
+      <c r="D14" t="s">
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G14" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="H14" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="J14" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="K14" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="O14" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1653,46 +1704,46 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15">
-        <v>14.4</v>
+        <v>171</v>
+      </c>
+      <c r="D15" t="s">
+        <v>172</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F15" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="G15" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="I15" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="K15" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O15" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1700,46 +1751,46 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" t="s">
+        <v>188</v>
+      </c>
+      <c r="J16" t="s">
+        <v>189</v>
+      </c>
+      <c r="K16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" t="s">
+        <v>190</v>
+      </c>
+      <c r="M16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16" t="s">
+        <v>191</v>
+      </c>
+      <c r="O16" t="s">
         <v>169</v>
-      </c>
-      <c r="C16" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16">
-        <v>7.6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>171</v>
-      </c>
-      <c r="F16" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" t="s">
-        <v>172</v>
-      </c>
-      <c r="H16" t="s">
-        <v>173</v>
-      </c>
-      <c r="I16" t="s">
-        <v>174</v>
-      </c>
-      <c r="J16" t="s">
-        <v>175</v>
-      </c>
-      <c r="K16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" t="s">
-        <v>176</v>
-      </c>
-      <c r="M16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16" t="s">
-        <v>177</v>
-      </c>
-      <c r="O16" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1747,46 +1798,46 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17">
-        <v>21</v>
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G17" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="H17" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I17" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="J17" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="K17" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1794,46 +1845,46 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18">
-        <v>19.88</v>
+        <v>204</v>
+      </c>
+      <c r="D18" t="s">
+        <v>205</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="F18" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="G18" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H18" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="I18" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="J18" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K18" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
